--- a/artfynd/A 56822-2025 artfynd.xlsx
+++ b/artfynd/A 56822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129666442</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129666404</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129666430</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129666455</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56822-2025 artfynd.xlsx
+++ b/artfynd/A 56822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129666442</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129666404</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129666430</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129666455</v>
       </c>
       <c r="B5" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56822-2025 artfynd.xlsx
+++ b/artfynd/A 56822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129666442</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129666404</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129666430</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129666455</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56822-2025 artfynd.xlsx
+++ b/artfynd/A 56822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129666442</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129666404</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129666430</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129666455</v>
       </c>
       <c r="B5" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56822-2025 artfynd.xlsx
+++ b/artfynd/A 56822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129666442</v>
       </c>
       <c r="B2" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129666404</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129666430</v>
+        <v>129666455</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500956</v>
+        <v>501110</v>
       </c>
       <c r="R4" t="n">
-        <v>6832334</v>
+        <v>6832835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129666455</v>
+        <v>129666430</v>
       </c>
       <c r="B5" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501110</v>
+        <v>500956</v>
       </c>
       <c r="R5" t="n">
-        <v>6832835</v>
+        <v>6832334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 56822-2025 artfynd.xlsx
+++ b/artfynd/A 56822-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129666455</v>
+        <v>129666430</v>
       </c>
       <c r="B4" t="n">
         <v>98790</v>
@@ -935,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501110</v>
+        <v>500956</v>
       </c>
       <c r="R4" t="n">
-        <v>6832835</v>
+        <v>6832334</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129666430</v>
+        <v>129666455</v>
       </c>
       <c r="B5" t="n">
         <v>98790</v>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500956</v>
+        <v>501110</v>
       </c>
       <c r="R5" t="n">
-        <v>6832334</v>
+        <v>6832835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 56822-2025 artfynd.xlsx
+++ b/artfynd/A 56822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129666442</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129666404</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129666430</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129666455</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56822-2025 artfynd.xlsx
+++ b/artfynd/A 56822-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129666430</v>
+        <v>129666455</v>
       </c>
       <c r="B4" t="n">
         <v>98794</v>
@@ -935,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500956</v>
+        <v>501110</v>
       </c>
       <c r="R4" t="n">
-        <v>6832334</v>
+        <v>6832835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129666455</v>
+        <v>129666430</v>
       </c>
       <c r="B5" t="n">
         <v>98794</v>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501110</v>
+        <v>500956</v>
       </c>
       <c r="R5" t="n">
-        <v>6832835</v>
+        <v>6832334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 56822-2025 artfynd.xlsx
+++ b/artfynd/A 56822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129666442</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129666404</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129666455</v>
+        <v>129666430</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501110</v>
+        <v>500956</v>
       </c>
       <c r="R4" t="n">
-        <v>6832835</v>
+        <v>6832334</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129666430</v>
+        <v>129666455</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500956</v>
+        <v>501110</v>
       </c>
       <c r="R5" t="n">
-        <v>6832334</v>
+        <v>6832835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 56822-2025 artfynd.xlsx
+++ b/artfynd/A 56822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129666442</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129666404</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129666430</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129666455</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56822-2025 artfynd.xlsx
+++ b/artfynd/A 56822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129666442</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129666404</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129666430</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129666455</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56822-2025 artfynd.xlsx
+++ b/artfynd/A 56822-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129666442</v>
+        <v>129666404</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501096</v>
+        <v>500994</v>
       </c>
       <c r="R2" t="n">
-        <v>6832846</v>
+        <v>6832343</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129666404</v>
+        <v>129666430</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500994</v>
+        <v>500956</v>
       </c>
       <c r="R3" t="n">
-        <v>6832343</v>
+        <v>6832334</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129666430</v>
+        <v>129666442</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500956</v>
+        <v>501096</v>
       </c>
       <c r="R4" t="n">
-        <v>6832334</v>
+        <v>6832846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1023,7 @@
         <v>129666455</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56822-2025 artfynd.xlsx
+++ b/artfynd/A 56822-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129666404</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129666430</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129666442</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,8 +1152,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129666455</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>